--- a/data/trans_bre/P1402-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1402-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,76</t>
+          <t>-5,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-64,09%</t>
+          <t>-63,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,45</t>
+          <t>-5,71; -0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,74</t>
+          <t>-3,25; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,89</t>
+          <t>-6,28; 0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -3,05</t>
+          <t>-8,53; -3,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-86,27; -2,72</t>
+          <t>-87,21; -13,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 97,36</t>
+          <t>-63,08; 94,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 20,32</t>
+          <t>-67,22; 15,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-78,47; -42,42</t>
+          <t>-77,14; -43,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,69</t>
+          <t>-6,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-73,6%</t>
+          <t>-71,97%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,13</t>
+          <t>-5,13; 0,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,2</t>
+          <t>-5,79; 0,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,85</t>
+          <t>-7,53; -1,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -4,21</t>
+          <t>-8,75; -3,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,5; 15,71</t>
+          <t>-82,78; 22,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 12,47</t>
+          <t>-79,67; 18,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,82; -10,11</t>
+          <t>-82,44; -15,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,09; -54,81</t>
+          <t>-83,88; -53,57</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>-12,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,22</t>
+          <t>-1,01; 8,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -1,0</t>
+          <t>-9,21; -1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 1,18</t>
+          <t>-8,32; 1,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 9,97</t>
+          <t>-6,03; 2,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 204,86</t>
+          <t>-16,95; 215,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,13; -9,38</t>
+          <t>-69,3; -10,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 17,42</t>
+          <t>-74,98; 22,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 290,78</t>
+          <t>-45,28; 26,92</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,44</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-57,69%</t>
+          <t>-48,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,8</t>
+          <t>-5,0; -0,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -0,66</t>
+          <t>-5,66; -0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -3,55</t>
+          <t>-8,08; -3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -4,06</t>
+          <t>-7,85; -3,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,57; -10,74</t>
+          <t>-58,91; -9,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,81; -8,78</t>
+          <t>-55,19; -7,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-73,78; -41,95</t>
+          <t>-73,52; -39,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,95; -39,88</t>
+          <t>-59,47; -33,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,7</t>
+          <t>-3,82; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,53</t>
+          <t>-0,79; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,02</t>
+          <t>-4,53; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,1</t>
+          <t>-0,08; 5,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,9; 60,62</t>
+          <t>-42,9; 64,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 108,72</t>
+          <t>-9,59; 108,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 21,37</t>
+          <t>-36,43; 21,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 54,16</t>
+          <t>-0,48; 79,65</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1276,17%</t>
+          <t>1242,33%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,43</t>
+          <t>9,05; 12,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,34</t>
+          <t>8,56; 14,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 15,53</t>
+          <t>10,24; 15,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,64</t>
+          <t>8,67; 12,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>155,6; 1697,11</t>
+          <t>146,35; 1859,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>298,16; 3729,84</t>
+          <t>303,59; 3953,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>279,87; 5812,83</t>
+          <t>380,34; 5109,91</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-17,42%</t>
+          <t>-16,4%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,24</t>
+          <t>-0,19; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,58</t>
+          <t>-0,32; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,95</t>
+          <t>-1,79; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,46</t>
+          <t>-2,77; -0,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 45,45</t>
+          <t>-3,1; 41,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 38,17</t>
+          <t>-3,77; 36,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 11,87</t>
+          <t>-18,74; 12,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 4,73</t>
+          <t>-27,2; -5,27</t>
         </is>
       </c>
     </row>
